--- a/layout/CORE_LayoutTenenciaAdicional_v3.3_Layout_TENENCIA_PRECIO.xlsx
+++ b/layout/CORE_LayoutTenenciaAdicional_v3.3_Layout_TENENCIA_PRECIO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LOCAL\DESA\non-purple-wheel\non-purple-wheel\layout\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD241504-A648-4C33-A5E9-2C1A84475E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B97315BB-B7D4-469D-BAD9-360332461AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3000" yWindow="1200" windowWidth="21600" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FILE_TENENCIA_PRECIO" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="43">
   <si>
     <t>TENENCIA</t>
   </si>
@@ -68,9 +68,6 @@
     <t>Catalogo</t>
   </si>
   <si>
-    <t>Comentario BW</t>
-  </si>
-  <si>
     <t>TITULOOBJETO</t>
   </si>
   <si>
@@ -110,9 +107,6 @@
     <t>Clave de la intencionalidad de la operación</t>
   </si>
   <si>
-    <t>Clasificacion Contable</t>
-  </si>
-  <si>
     <t>Restriccion</t>
   </si>
   <si>
@@ -167,7 +161,10 @@
     <t>Debe ser una fecha valida</t>
   </si>
   <si>
-    <t>AAAAMMDD</t>
+    <t>C_CLAS_CONTABLE_TEN</t>
+  </si>
+  <si>
+    <t>AAAA/MM/DD</t>
   </si>
 </sst>
 </file>
@@ -231,6 +228,7 @@
     <font>
       <sz val="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -351,8 +349,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table2457109104" displayName="Table2457109104" ref="A1:J12" totalsRowShown="0">
-  <tableColumns count="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table2457109104" displayName="Table2457109104" ref="A1:I12" totalsRowShown="0">
+  <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Orden"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Nombre"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Tipo"/>
@@ -362,7 +360,6 @@
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Descripcion"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Validacion"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Catalogo"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Comentario BW"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -665,21 +662,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.88671875" customWidth="1"/>
-    <col min="3" max="3" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.88671875" customWidth="1"/>
+    <col min="1" max="1" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" customWidth="1"/>
     <col min="7" max="7" width="31" customWidth="1"/>
-    <col min="8" max="8" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -707,293 +704,289 @@
       <c r="I1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" t="s">
-        <v>10</v>
-      </c>
     </row>
-    <row r="2" spans="1:10" ht="28.2" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="27" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="D2" s="2">
         <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
         <v>14</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>15</v>
       </c>
-      <c r="I2" t="s">
-        <v>16</v>
-      </c>
     </row>
-    <row r="3" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="E3" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
         <v>20</v>
       </c>
-      <c r="H3" t="s">
-        <v>21</v>
-      </c>
     </row>
-    <row r="4" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" s="5">
         <v>2</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="39" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" s="5">
         <v>2</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D6" s="2">
         <v>6</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J6" s="4"/>
+        <v>27</v>
+      </c>
     </row>
-    <row r="7" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
         <v>0</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D8" s="2">
         <v>6</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s">
         <v>0</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D9">
         <v>12</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F9" t="s">
         <v>0</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I9" s="4"/>
     </row>
-    <row r="10" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D10">
         <v>12</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s">
         <v>0</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I10" s="4"/>
     </row>
-    <row r="11" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D11">
         <v>12</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F11" t="s">
         <v>0</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="10"/>
       <c r="G12" s="10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1006,26 +999,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cf35dce2-b600-471d-a6b0-9e8301b7851b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3de82841-ffbb-418b-a888-39c303bacd30" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101003EADB6AB950C774BBB9F1C75E500B284" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="101bf262c701ad3b79067f76f13f8957">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cf35dce2-b600-471d-a6b0-9e8301b7851b" xmlns:ns3="3de82841-ffbb-418b-a888-39c303bacd30" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a75b904d2a00e23a3c27f0f1b23bc34b" ns2:_="" ns3:_="">
     <xsd:import namespace="cf35dce2-b600-471d-a6b0-9e8301b7851b"/>
@@ -1226,26 +1199,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73BC83AF-6FA7-4B3A-A6A1-D0D3163B7E5B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{042DEAB4-1147-45FE-A2A8-66DE256BE400}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="cf35dce2-b600-471d-a6b0-9e8301b7851b"/>
-    <ds:schemaRef ds:uri="3de82841-ffbb-418b-a888-39c303bacd30"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cf35dce2-b600-471d-a6b0-9e8301b7851b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3de82841-ffbb-418b-a888-39c303bacd30" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07F8EC51-43B2-47FB-893E-4F991F6E884D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1262,4 +1236,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73BC83AF-6FA7-4B3A-A6A1-D0D3163B7E5B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{042DEAB4-1147-45FE-A2A8-66DE256BE400}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="cf35dce2-b600-471d-a6b0-9e8301b7851b"/>
+    <ds:schemaRef ds:uri="3de82841-ffbb-418b-a888-39c303bacd30"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>